--- a/data/trans_orig/P25D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40674</t>
+          <t>41972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>31519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40342</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68140</t>
+          <t>64422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12613</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>12182</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>7257</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>19813</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>12182</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>6941</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>19612</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12186</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>376</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>13667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38900</t>
+          <t>42576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37314</t>
+          <t>41434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>553515</t>
+          <t>550577</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>594330</t>
+          <t>594072</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>630587</t>
+          <t>629844</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>647735</t>
+          <t>647584</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1194524</t>
+          <t>1186585</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1237450</t>
+          <t>1236245</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42965</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>27652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49524</t>
+          <t>49832</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>43357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81584</t>
+          <t>81856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29396</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19308</t>
+          <t>18628</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16186</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40851</t>
+          <t>42248</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>18384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37295</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40986</t>
+          <t>42977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>682023</t>
+          <t>736512</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>859906</t>
+          <t>862683</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>470822</t>
+          <t>423223</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1101608</t>
+          <t>1099694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>876738</t>
+          <t>878467</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>908325</t>
+          <t>907685</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1193630</t>
+          <t>1195851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1999703</t>
+          <t>1994864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36782</t>
+          <t>37478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29342</t>
+          <t>33298</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74874</t>
+          <t>78319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30324</t>
+          <t>30948</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>39129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24323</t>
+          <t>24449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31623</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>23128</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>609420</t>
+          <t>606470</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654856</t>
+          <t>652479</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>863648</t>
+          <t>864534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>911053</t>
+          <t>912302</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1487827</t>
+          <t>1485085</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1559977</t>
+          <t>1562133</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41625</t>
+          <t>41279</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22364</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46150</t>
+          <t>45578</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44634</t>
+          <t>44472</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79438</t>
+          <t>79340</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19937</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9621</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40155</t>
+          <t>42011</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50048</t>
+          <t>47781</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>35312</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28660</t>
+          <t>28705</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>831659</t>
+          <t>831657</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>869222</t>
+          <t>870838</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>998230</t>
+          <t>996378</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1038066</t>
+          <t>1037584</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1843632</t>
+          <t>1842233</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1897430</t>
+          <t>1901019</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>83247</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>140157</t>
+          <t>141201</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>90221</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>135696</t>
+          <t>137908</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>188496</t>
+          <t>187718</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>263382</t>
+          <t>261841</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>34956</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>71688</t>
+          <t>72530</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>61179</t>
+          <t>63309</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,47 +4073,47 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>92141</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>118721</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>92141</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>72536</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>119429</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>57918</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>44527</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>82700</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23296</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>59954</t>
+          <t>60266</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>37248</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>84690</t>
+          <t>88272</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>28008</t>
+          <t>31103</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1047477</t>
+          <t>1088058</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>42891</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1254547</t>
+          <t>1207587</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2225465</t>
+          <t>2168112</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3173963</t>
+          <t>3166776</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3403309</t>
+          <t>3398691</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3481354</t>
+          <t>3480319</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5529591</t>
+          <t>5575882</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6621651</t>
+          <t>6621270</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27896</t>
+          <t>29582</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41972</t>
+          <t>44231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16413</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31519</t>
+          <t>32122</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>50416</t>
+          <t>53328</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>42367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64422</t>
+          <t>69159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>13340</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42576</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,67 +1212,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>11361</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3552</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>24857</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>13647</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>41434</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>579241</t>
+          <t>633609</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>550577</t>
+          <t>613898</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>594072</t>
+          <t>648365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>639326</t>
+          <t>694589</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>629844</t>
+          <t>684407</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>647584</t>
+          <t>703615</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1218568</t>
+          <t>1328198</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1186585</t>
+          <t>1304640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1236245</t>
+          <t>1345024</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>633158</t>
+          <t>688368</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>633158</t>
+          <t>688368</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>633158</t>
+          <t>688368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>673951</t>
+          <t>731064</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>673951</t>
+          <t>731064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>673951</t>
+          <t>731064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1307109</t>
+          <t>1419432</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1307109</t>
+          <t>1419432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1307109</t>
+          <t>1419432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>30365</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>45104</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36037</t>
+          <t>42222</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>57189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>62313</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43357</t>
+          <t>58267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81856</t>
+          <t>92591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1633,102 +1633,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>17673</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>30783</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>11148</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6320</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19141</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>28821</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>18924</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>44134</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10621</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5970</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18628</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>26785</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>16059</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>42248</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>39925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>29062</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42977</t>
+          <t>49119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>255262</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>736512</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>257678</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>862683</t>
+          <t>28509</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>868595</t>
+          <t>958889</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>423223</t>
+          <t>933230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1099694</t>
+          <t>980614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>894279</t>
+          <t>999224</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>878467</t>
+          <t>981256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>907685</t>
+          <t>1015140</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1762875</t>
+          <t>1958113</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1195851</t>
+          <t>1928322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1994864</t>
+          <t>1983611</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>957527</t>
+          <t>1070150</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>957527</t>
+          <t>1070150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>957527</t>
+          <t>1070150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2150391</t>
+          <t>2119067</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2150391</t>
+          <t>2119067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2150391</t>
+          <t>2119067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31039</t>
+          <t>31558</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>49332</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37478</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>53041</t>
+          <t>56739</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33298</t>
+          <t>39538</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78319</t>
+          <t>79486</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>16227</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>37792</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25672</t>
+          <t>31320</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39129</t>
+          <t>45656</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24449</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>32525</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24835</t>
+          <t>25964</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16330</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>26036</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>632758</t>
+          <t>721630</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>606470</t>
+          <t>696965</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652479</t>
+          <t>740744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>886065</t>
+          <t>758237</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>864534</t>
+          <t>739396</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>912302</t>
+          <t>772426</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1518822</t>
+          <t>1479867</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1485085</t>
+          <t>1450551</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1562133</t>
+          <t>1505460</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,17 +3110,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>27760</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>18803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41279</t>
+          <t>42398</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>32519</t>
+          <t>34431</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22733</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45578</t>
+          <t>47823</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>58483</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79340</t>
+          <t>79785</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>24488</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47781</t>
+          <t>36546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>35312</t>
+          <t>44445</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>15455</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28705</t>
+          <t>32283</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -3562,22 +3562,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>24119</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>17785</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>32276</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>853398</t>
+          <t>908567</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>831657</t>
+          <t>886209</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>870838</t>
+          <t>928026</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1020224</t>
+          <t>1040830</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>996378</t>
+          <t>1022577</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1037584</t>
+          <t>1054636</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1873621</t>
+          <t>1949397</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1842233</t>
+          <t>1922093</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1901019</t>
+          <t>1973475</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>919761</t>
+          <t>982782</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>919761</t>
+          <t>982782</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>919761</t>
+          <t>982782</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1090666</t>
+          <t>1114597</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1090666</t>
+          <t>1114597</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1090666</t>
+          <t>1114597</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2010427</t>
+          <t>2097379</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2010427</t>
+          <t>2097379</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2010427</t>
+          <t>2097379</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>111174</t>
+          <t>119264</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>96483</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>141201</t>
+          <t>147680</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>113078</t>
+          <t>125579</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>90221</t>
+          <t>105367</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>137908</t>
+          <t>149934</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>224253</t>
+          <t>244844</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>187718</t>
+          <t>211190</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>261841</t>
+          <t>276669</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4018,67 +4018,67 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>51381</t>
+          <t>60309</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>34956</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72530</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>37660</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>27356</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>48890</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>40760</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>28501</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>63309</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,27 +4088,27 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>92141</t>
+          <t>97968</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>73000</t>
+          <t>80404</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>118721</t>
+          <t>120988</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>36286</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>81536</t>
+          <t>92172</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>29843</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>68914</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>37248</t>
+          <t>39993</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>60953</t>
+          <t>71078</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>44132</t>
+          <t>51980</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>88272</t>
+          <t>93838</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4357,69 +4357,69 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>278232</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1088058</t>
+          <t>57652</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>19723</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>11981</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>33565</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>15192</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>8357</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>28950</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>293424</t>
+          <t>52017</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1207587</t>
+          <t>78056</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2933993</t>
+          <t>3222696</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2168112</t>
+          <t>3173821</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3166776</t>
+          <t>3261218</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3439894</t>
+          <t>3492880</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3398691</t>
+          <t>3459627</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3480319</t>
+          <t>3520318</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>6373886</t>
+          <t>6715575</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5575882</t>
+          <t>6665986</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6621270</t>
+          <t>6768208</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
